--- a/docs/EEG_kit_BOM_INTERNAL_RevC_costed.xlsx
+++ b/docs/EEG_kit_BOM_INTERNAL_RevC_costed.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kit summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Kit summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev C, 1 September 2026.  Companion to RFQ-EEG-001 Rev E and DSN-EEG-003 Rev C.</t>
+          <t>Rev C, 1 September 2026.  Companion to RFQ-EEG-001 Rev E and DSN-EEG-003 Rev D.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>JIG-EEG-009 Rev B specifies more fixtures than v1 assumed. Held at v1's figure until JIG-EEG-009 section 6.1 is quoted.</t>
+          <t>JIG-EEG-009 Rev C specifies more fixtures than v1 assumed. Held at v1's figure until JIG-EEG-009 section 6.1 is quoted.</t>
         </is>
       </c>
     </row>
